--- a/tests/reports/validation_test_300_report.xlsx
+++ b/tests/reports/validation_test_300_report.xlsx
@@ -2810,7 +2810,7 @@
         <v>36</v>
       </c>
       <c r="J2" s="6">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>37</v>
@@ -2848,7 +2848,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="8">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>37</v>
@@ -2886,7 +2886,7 @@
         <v>50</v>
       </c>
       <c r="J4" s="6">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>37</v>
@@ -2924,7 +2924,7 @@
         <v>56</v>
       </c>
       <c r="J5" s="8">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>37</v>
@@ -2962,7 +2962,7 @@
         <v>36</v>
       </c>
       <c r="J6" s="6">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>37</v>
@@ -3000,7 +3000,7 @@
         <v>44</v>
       </c>
       <c r="J7" s="8">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>37</v>
@@ -3038,7 +3038,7 @@
         <v>50</v>
       </c>
       <c r="J8" s="6">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>37</v>
@@ -3076,7 +3076,7 @@
         <v>56</v>
       </c>
       <c r="J9" s="8">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>37</v>
@@ -3114,7 +3114,7 @@
         <v>36</v>
       </c>
       <c r="J10" s="6">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>37</v>
@@ -3152,7 +3152,7 @@
         <v>44</v>
       </c>
       <c r="J11" s="8">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>37</v>
@@ -3190,7 +3190,7 @@
         <v>50</v>
       </c>
       <c r="J12" s="6">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>37</v>
@@ -3228,7 +3228,7 @@
         <v>56</v>
       </c>
       <c r="J13" s="8">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>37</v>
@@ -3266,7 +3266,7 @@
         <v>36</v>
       </c>
       <c r="J14" s="6">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>37</v>
@@ -3304,7 +3304,7 @@
         <v>44</v>
       </c>
       <c r="J15" s="8">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>37</v>
@@ -3342,7 +3342,7 @@
         <v>50</v>
       </c>
       <c r="J16" s="6">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="K16" s="5" t="s">
         <v>37</v>
@@ -3380,7 +3380,7 @@
         <v>56</v>
       </c>
       <c r="J17" s="8">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="K17" s="9" t="s">
         <v>37</v>
@@ -3418,7 +3418,7 @@
         <v>36</v>
       </c>
       <c r="J18" s="6">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>37</v>
@@ -3456,7 +3456,7 @@
         <v>44</v>
       </c>
       <c r="J19" s="8">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>37</v>
@@ -3494,7 +3494,7 @@
         <v>50</v>
       </c>
       <c r="J20" s="6">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>37</v>
@@ -3532,7 +3532,7 @@
         <v>56</v>
       </c>
       <c r="J21" s="8">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>37</v>
@@ -3570,7 +3570,7 @@
         <v>36</v>
       </c>
       <c r="J22" s="6">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>37</v>
@@ -3608,7 +3608,7 @@
         <v>44</v>
       </c>
       <c r="J23" s="8">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>37</v>
@@ -3646,7 +3646,7 @@
         <v>50</v>
       </c>
       <c r="J24" s="6">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>37</v>
@@ -3684,7 +3684,7 @@
         <v>56</v>
       </c>
       <c r="J25" s="8">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>37</v>
@@ -3722,7 +3722,7 @@
         <v>36</v>
       </c>
       <c r="J26" s="6">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>37</v>
@@ -3760,7 +3760,7 @@
         <v>44</v>
       </c>
       <c r="J27" s="8">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>37</v>
@@ -3798,7 +3798,7 @@
         <v>50</v>
       </c>
       <c r="J28" s="6">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="K28" s="5" t="s">
         <v>37</v>
@@ -3836,7 +3836,7 @@
         <v>56</v>
       </c>
       <c r="J29" s="8">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>37</v>
@@ -3874,7 +3874,7 @@
         <v>36</v>
       </c>
       <c r="J30" s="6">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>37</v>
@@ -3912,7 +3912,7 @@
         <v>44</v>
       </c>
       <c r="J31" s="8">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>37</v>
@@ -3950,7 +3950,7 @@
         <v>50</v>
       </c>
       <c r="J32" s="6">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>37</v>
@@ -3988,7 +3988,7 @@
         <v>56</v>
       </c>
       <c r="J33" s="8">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>37</v>
@@ -4026,7 +4026,7 @@
         <v>36</v>
       </c>
       <c r="J34" s="6">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="K34" s="5" t="s">
         <v>37</v>
@@ -4064,7 +4064,7 @@
         <v>44</v>
       </c>
       <c r="J35" s="8">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="K35" s="9" t="s">
         <v>37</v>
@@ -4102,7 +4102,7 @@
         <v>50</v>
       </c>
       <c r="J36" s="6">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="K36" s="5" t="s">
         <v>37</v>
@@ -4140,7 +4140,7 @@
         <v>56</v>
       </c>
       <c r="J37" s="8">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="K37" s="9" t="s">
         <v>37</v>
@@ -4178,7 +4178,7 @@
         <v>36</v>
       </c>
       <c r="J38" s="6">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="K38" s="5" t="s">
         <v>37</v>
@@ -4216,7 +4216,7 @@
         <v>44</v>
       </c>
       <c r="J39" s="8">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="K39" s="9" t="s">
         <v>37</v>
@@ -4254,7 +4254,7 @@
         <v>50</v>
       </c>
       <c r="J40" s="6">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="K40" s="5" t="s">
         <v>37</v>
@@ -4292,7 +4292,7 @@
         <v>56</v>
       </c>
       <c r="J41" s="8">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>37</v>
@@ -4330,7 +4330,7 @@
         <v>36</v>
       </c>
       <c r="J42" s="6">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="K42" s="5" t="s">
         <v>37</v>
@@ -4368,7 +4368,7 @@
         <v>44</v>
       </c>
       <c r="J43" s="8">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="K43" s="9" t="s">
         <v>37</v>
@@ -4406,7 +4406,7 @@
         <v>50</v>
       </c>
       <c r="J44" s="6">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="K44" s="5" t="s">
         <v>37</v>
@@ -4444,7 +4444,7 @@
         <v>56</v>
       </c>
       <c r="J45" s="8">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="K45" s="9" t="s">
         <v>37</v>
@@ -4482,7 +4482,7 @@
         <v>36</v>
       </c>
       <c r="J46" s="6">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="K46" s="5" t="s">
         <v>37</v>
@@ -4520,7 +4520,7 @@
         <v>44</v>
       </c>
       <c r="J47" s="8">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>37</v>
@@ -4558,7 +4558,7 @@
         <v>50</v>
       </c>
       <c r="J48" s="6">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="K48" s="5" t="s">
         <v>37</v>
@@ -4596,7 +4596,7 @@
         <v>56</v>
       </c>
       <c r="J49" s="8">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="K49" s="9" t="s">
         <v>37</v>
@@ -4634,7 +4634,7 @@
         <v>36</v>
       </c>
       <c r="J50" s="6">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="K50" s="5" t="s">
         <v>37</v>
@@ -4672,7 +4672,7 @@
         <v>44</v>
       </c>
       <c r="J51" s="8">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="K51" s="9" t="s">
         <v>37</v>
@@ -4710,7 +4710,7 @@
         <v>50</v>
       </c>
       <c r="J52" s="6">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="K52" s="5" t="s">
         <v>37</v>
@@ -4748,7 +4748,7 @@
         <v>56</v>
       </c>
       <c r="J53" s="8">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K53" s="9" t="s">
         <v>37</v>
@@ -4786,7 +4786,7 @@
         <v>36</v>
       </c>
       <c r="J54" s="6">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="K54" s="5" t="s">
         <v>37</v>
@@ -4824,7 +4824,7 @@
         <v>44</v>
       </c>
       <c r="J55" s="8">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="K55" s="9" t="s">
         <v>37</v>
@@ -4862,7 +4862,7 @@
         <v>50</v>
       </c>
       <c r="J56" s="6">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="K56" s="5" t="s">
         <v>37</v>
@@ -4900,7 +4900,7 @@
         <v>56</v>
       </c>
       <c r="J57" s="8">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="K57" s="9" t="s">
         <v>37</v>
@@ -4938,7 +4938,7 @@
         <v>36</v>
       </c>
       <c r="J58" s="6">
-        <v>141</v>
+        <v>30</v>
       </c>
       <c r="K58" s="5" t="s">
         <v>37</v>
@@ -4976,7 +4976,7 @@
         <v>44</v>
       </c>
       <c r="J59" s="8">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c r="K59" s="9" t="s">
         <v>37</v>
@@ -5014,7 +5014,7 @@
         <v>50</v>
       </c>
       <c r="J60" s="6">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="K60" s="5" t="s">
         <v>37</v>
@@ -5052,7 +5052,7 @@
         <v>56</v>
       </c>
       <c r="J61" s="8">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="K61" s="9" t="s">
         <v>37</v>
@@ -5090,7 +5090,7 @@
         <v>36</v>
       </c>
       <c r="J62" s="6">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="K62" s="5" t="s">
         <v>37</v>
@@ -5128,7 +5128,7 @@
         <v>44</v>
       </c>
       <c r="J63" s="8">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="K63" s="9" t="s">
         <v>37</v>
@@ -5166,7 +5166,7 @@
         <v>50</v>
       </c>
       <c r="J64" s="6">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="K64" s="5" t="s">
         <v>37</v>
@@ -5204,7 +5204,7 @@
         <v>56</v>
       </c>
       <c r="J65" s="8">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="K65" s="9" t="s">
         <v>37</v>
@@ -5242,7 +5242,7 @@
         <v>36</v>
       </c>
       <c r="J66" s="6">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="K66" s="5" t="s">
         <v>37</v>
@@ -5280,7 +5280,7 @@
         <v>44</v>
       </c>
       <c r="J67" s="8">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="K67" s="9" t="s">
         <v>37</v>
@@ -5318,7 +5318,7 @@
         <v>50</v>
       </c>
       <c r="J68" s="6">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="K68" s="5" t="s">
         <v>37</v>
@@ -5356,7 +5356,7 @@
         <v>56</v>
       </c>
       <c r="J69" s="8">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K69" s="9" t="s">
         <v>37</v>
@@ -5394,7 +5394,7 @@
         <v>36</v>
       </c>
       <c r="J70" s="6">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="K70" s="5" t="s">
         <v>37</v>
@@ -5432,7 +5432,7 @@
         <v>44</v>
       </c>
       <c r="J71" s="8">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K71" s="9" t="s">
         <v>37</v>
@@ -5470,7 +5470,7 @@
         <v>50</v>
       </c>
       <c r="J72" s="6">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="K72" s="5" t="s">
         <v>37</v>
@@ -5508,7 +5508,7 @@
         <v>56</v>
       </c>
       <c r="J73" s="8">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="K73" s="9" t="s">
         <v>37</v>
@@ -5546,7 +5546,7 @@
         <v>36</v>
       </c>
       <c r="J74" s="6">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="K74" s="5" t="s">
         <v>37</v>
@@ -5584,7 +5584,7 @@
         <v>44</v>
       </c>
       <c r="J75" s="8">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="K75" s="9" t="s">
         <v>37</v>
@@ -5622,7 +5622,7 @@
         <v>50</v>
       </c>
       <c r="J76" s="6">
-        <v>140</v>
+        <v>36</v>
       </c>
       <c r="K76" s="5" t="s">
         <v>37</v>
@@ -5660,7 +5660,7 @@
         <v>56</v>
       </c>
       <c r="J77" s="8">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="K77" s="9" t="s">
         <v>37</v>
@@ -5698,7 +5698,7 @@
         <v>36</v>
       </c>
       <c r="J78" s="6">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="K78" s="5" t="s">
         <v>37</v>
@@ -5736,7 +5736,7 @@
         <v>44</v>
       </c>
       <c r="J79" s="8">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="K79" s="9" t="s">
         <v>37</v>
@@ -5774,7 +5774,7 @@
         <v>50</v>
       </c>
       <c r="J80" s="6">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="K80" s="5" t="s">
         <v>37</v>
@@ -5812,7 +5812,7 @@
         <v>56</v>
       </c>
       <c r="J81" s="8">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="K81" s="9" t="s">
         <v>37</v>
@@ -5850,7 +5850,7 @@
         <v>36</v>
       </c>
       <c r="J82" s="6">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="K82" s="5" t="s">
         <v>37</v>
@@ -5888,7 +5888,7 @@
         <v>44</v>
       </c>
       <c r="J83" s="8">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="K83" s="9" t="s">
         <v>37</v>
@@ -5926,7 +5926,7 @@
         <v>50</v>
       </c>
       <c r="J84" s="6">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="K84" s="5" t="s">
         <v>37</v>
@@ -5964,7 +5964,7 @@
         <v>56</v>
       </c>
       <c r="J85" s="8">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="K85" s="9" t="s">
         <v>37</v>
@@ -6002,7 +6002,7 @@
         <v>36</v>
       </c>
       <c r="J86" s="6">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="K86" s="5" t="s">
         <v>37</v>
@@ -6040,7 +6040,7 @@
         <v>44</v>
       </c>
       <c r="J87" s="8">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="K87" s="9" t="s">
         <v>37</v>
@@ -6078,7 +6078,7 @@
         <v>50</v>
       </c>
       <c r="J88" s="6">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="K88" s="5" t="s">
         <v>37</v>
@@ -6116,7 +6116,7 @@
         <v>56</v>
       </c>
       <c r="J89" s="8">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="K89" s="9" t="s">
         <v>37</v>
@@ -6154,7 +6154,7 @@
         <v>36</v>
       </c>
       <c r="J90" s="6">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="K90" s="5" t="s">
         <v>37</v>
@@ -6192,7 +6192,7 @@
         <v>44</v>
       </c>
       <c r="J91" s="8">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="K91" s="9" t="s">
         <v>37</v>
@@ -6230,7 +6230,7 @@
         <v>50</v>
       </c>
       <c r="J92" s="6">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="K92" s="5" t="s">
         <v>37</v>
@@ -6268,7 +6268,7 @@
         <v>56</v>
       </c>
       <c r="J93" s="8">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="K93" s="9" t="s">
         <v>37</v>
@@ -6306,7 +6306,7 @@
         <v>36</v>
       </c>
       <c r="J94" s="6">
-        <v>126</v>
+        <v>34</v>
       </c>
       <c r="K94" s="5" t="s">
         <v>37</v>
@@ -6344,7 +6344,7 @@
         <v>44</v>
       </c>
       <c r="J95" s="8">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="K95" s="9" t="s">
         <v>37</v>
@@ -6382,7 +6382,7 @@
         <v>50</v>
       </c>
       <c r="J96" s="6">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="K96" s="5" t="s">
         <v>37</v>
@@ -6420,7 +6420,7 @@
         <v>56</v>
       </c>
       <c r="J97" s="8">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K97" s="9" t="s">
         <v>37</v>
@@ -6458,7 +6458,7 @@
         <v>36</v>
       </c>
       <c r="J98" s="6">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="K98" s="5" t="s">
         <v>37</v>
@@ -6496,7 +6496,7 @@
         <v>44</v>
       </c>
       <c r="J99" s="8">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="K99" s="9" t="s">
         <v>37</v>
@@ -6534,7 +6534,7 @@
         <v>50</v>
       </c>
       <c r="J100" s="6">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="K100" s="5" t="s">
         <v>37</v>
@@ -6572,7 +6572,7 @@
         <v>56</v>
       </c>
       <c r="J101" s="8">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="K101" s="9" t="s">
         <v>37</v>
@@ -6610,7 +6610,7 @@
         <v>36</v>
       </c>
       <c r="J102" s="6">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="K102" s="5" t="s">
         <v>37</v>
@@ -6648,7 +6648,7 @@
         <v>44</v>
       </c>
       <c r="J103" s="8">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K103" s="9" t="s">
         <v>37</v>
@@ -6686,7 +6686,7 @@
         <v>50</v>
       </c>
       <c r="J104" s="6">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="K104" s="5" t="s">
         <v>37</v>
@@ -6724,7 +6724,7 @@
         <v>56</v>
       </c>
       <c r="J105" s="8">
-        <v>144</v>
+        <v>89</v>
       </c>
       <c r="K105" s="9" t="s">
         <v>37</v>
@@ -6762,7 +6762,7 @@
         <v>36</v>
       </c>
       <c r="J106" s="6">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K106" s="5" t="s">
         <v>37</v>
@@ -6800,7 +6800,7 @@
         <v>44</v>
       </c>
       <c r="J107" s="8">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="K107" s="9" t="s">
         <v>37</v>
@@ -6838,7 +6838,7 @@
         <v>50</v>
       </c>
       <c r="J108" s="6">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="K108" s="5" t="s">
         <v>37</v>
@@ -6876,7 +6876,7 @@
         <v>56</v>
       </c>
       <c r="J109" s="8">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="K109" s="9" t="s">
         <v>37</v>
@@ -6914,7 +6914,7 @@
         <v>36</v>
       </c>
       <c r="J110" s="6">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="K110" s="5" t="s">
         <v>37</v>
@@ -6952,7 +6952,7 @@
         <v>44</v>
       </c>
       <c r="J111" s="8">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="K111" s="9" t="s">
         <v>37</v>
@@ -6990,7 +6990,7 @@
         <v>50</v>
       </c>
       <c r="J112" s="6">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="K112" s="5" t="s">
         <v>37</v>
@@ -7028,7 +7028,7 @@
         <v>56</v>
       </c>
       <c r="J113" s="8">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="K113" s="9" t="s">
         <v>37</v>
@@ -7066,7 +7066,7 @@
         <v>36</v>
       </c>
       <c r="J114" s="6">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K114" s="5" t="s">
         <v>37</v>
@@ -7104,7 +7104,7 @@
         <v>44</v>
       </c>
       <c r="J115" s="8">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="K115" s="9" t="s">
         <v>37</v>
@@ -7142,7 +7142,7 @@
         <v>50</v>
       </c>
       <c r="J116" s="6">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="K116" s="5" t="s">
         <v>37</v>
@@ -7180,7 +7180,7 @@
         <v>56</v>
       </c>
       <c r="J117" s="8">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="K117" s="9" t="s">
         <v>37</v>
@@ -7218,7 +7218,7 @@
         <v>36</v>
       </c>
       <c r="J118" s="6">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="K118" s="5" t="s">
         <v>37</v>
@@ -7256,7 +7256,7 @@
         <v>44</v>
       </c>
       <c r="J119" s="8">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="K119" s="9" t="s">
         <v>37</v>
@@ -7294,7 +7294,7 @@
         <v>50</v>
       </c>
       <c r="J120" s="6">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="K120" s="5" t="s">
         <v>37</v>
@@ -7332,7 +7332,7 @@
         <v>56</v>
       </c>
       <c r="J121" s="8">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="K121" s="9" t="s">
         <v>37</v>
@@ -7370,7 +7370,7 @@
         <v>36</v>
       </c>
       <c r="J122" s="6">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="K122" s="5" t="s">
         <v>37</v>
@@ -7408,7 +7408,7 @@
         <v>44</v>
       </c>
       <c r="J123" s="8">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="K123" s="9" t="s">
         <v>37</v>
@@ -7446,7 +7446,7 @@
         <v>50</v>
       </c>
       <c r="J124" s="6">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="K124" s="5" t="s">
         <v>37</v>
@@ -7484,7 +7484,7 @@
         <v>56</v>
       </c>
       <c r="J125" s="8">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="K125" s="9" t="s">
         <v>37</v>
@@ -7522,7 +7522,7 @@
         <v>36</v>
       </c>
       <c r="J126" s="6">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="K126" s="5" t="s">
         <v>37</v>
@@ -7560,7 +7560,7 @@
         <v>44</v>
       </c>
       <c r="J127" s="8">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="K127" s="9" t="s">
         <v>37</v>
@@ -7598,7 +7598,7 @@
         <v>50</v>
       </c>
       <c r="J128" s="6">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="K128" s="5" t="s">
         <v>37</v>
@@ -7636,7 +7636,7 @@
         <v>56</v>
       </c>
       <c r="J129" s="8">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="K129" s="9" t="s">
         <v>37</v>
@@ -7674,7 +7674,7 @@
         <v>36</v>
       </c>
       <c r="J130" s="6">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="K130" s="5" t="s">
         <v>37</v>
@@ -7712,7 +7712,7 @@
         <v>44</v>
       </c>
       <c r="J131" s="8">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K131" s="9" t="s">
         <v>37</v>
@@ -7750,7 +7750,7 @@
         <v>50</v>
       </c>
       <c r="J132" s="6">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="K132" s="5" t="s">
         <v>37</v>
@@ -7788,7 +7788,7 @@
         <v>56</v>
       </c>
       <c r="J133" s="8">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="K133" s="9" t="s">
         <v>37</v>
@@ -7826,7 +7826,7 @@
         <v>36</v>
       </c>
       <c r="J134" s="6">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="K134" s="5" t="s">
         <v>37</v>
@@ -7864,7 +7864,7 @@
         <v>44</v>
       </c>
       <c r="J135" s="8">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="K135" s="9" t="s">
         <v>37</v>
@@ -7902,7 +7902,7 @@
         <v>50</v>
       </c>
       <c r="J136" s="6">
-        <v>148</v>
+        <v>93</v>
       </c>
       <c r="K136" s="5" t="s">
         <v>37</v>
@@ -7940,7 +7940,7 @@
         <v>56</v>
       </c>
       <c r="J137" s="8">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="K137" s="9" t="s">
         <v>37</v>
@@ -7978,7 +7978,7 @@
         <v>36</v>
       </c>
       <c r="J138" s="6">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="K138" s="5" t="s">
         <v>37</v>
@@ -8016,7 +8016,7 @@
         <v>44</v>
       </c>
       <c r="J139" s="8">
-        <v>149</v>
+        <v>62</v>
       </c>
       <c r="K139" s="9" t="s">
         <v>37</v>
@@ -8054,7 +8054,7 @@
         <v>50</v>
       </c>
       <c r="J140" s="6">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="K140" s="5" t="s">
         <v>37</v>
@@ -8092,7 +8092,7 @@
         <v>56</v>
       </c>
       <c r="J141" s="8">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="K141" s="9" t="s">
         <v>37</v>
@@ -8130,7 +8130,7 @@
         <v>36</v>
       </c>
       <c r="J142" s="6">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="K142" s="5" t="s">
         <v>37</v>
@@ -8168,7 +8168,7 @@
         <v>44</v>
       </c>
       <c r="J143" s="8">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="K143" s="9" t="s">
         <v>37</v>
@@ -8206,7 +8206,7 @@
         <v>50</v>
       </c>
       <c r="J144" s="6">
-        <v>135</v>
+        <v>46</v>
       </c>
       <c r="K144" s="5" t="s">
         <v>37</v>
@@ -8244,7 +8244,7 @@
         <v>56</v>
       </c>
       <c r="J145" s="8">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="K145" s="9" t="s">
         <v>37</v>
@@ -8282,7 +8282,7 @@
         <v>36</v>
       </c>
       <c r="J146" s="6">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="K146" s="5" t="s">
         <v>37</v>
@@ -8320,7 +8320,7 @@
         <v>44</v>
       </c>
       <c r="J147" s="8">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K147" s="9" t="s">
         <v>37</v>
@@ -8358,7 +8358,7 @@
         <v>50</v>
       </c>
       <c r="J148" s="6">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="K148" s="5" t="s">
         <v>37</v>
@@ -8396,7 +8396,7 @@
         <v>56</v>
       </c>
       <c r="J149" s="8">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="K149" s="9" t="s">
         <v>37</v>
@@ -8434,7 +8434,7 @@
         <v>36</v>
       </c>
       <c r="J150" s="6">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="K150" s="5" t="s">
         <v>37</v>
@@ -8472,7 +8472,7 @@
         <v>44</v>
       </c>
       <c r="J151" s="8">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="K151" s="9" t="s">
         <v>37</v>
@@ -8510,7 +8510,7 @@
         <v>50</v>
       </c>
       <c r="J152" s="6">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="K152" s="5" t="s">
         <v>37</v>
@@ -8548,7 +8548,7 @@
         <v>56</v>
       </c>
       <c r="J153" s="8">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="K153" s="9" t="s">
         <v>37</v>
@@ -8586,7 +8586,7 @@
         <v>36</v>
       </c>
       <c r="J154" s="6">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="K154" s="5" t="s">
         <v>37</v>
@@ -8624,7 +8624,7 @@
         <v>44</v>
       </c>
       <c r="J155" s="8">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="K155" s="9" t="s">
         <v>37</v>
@@ -8662,7 +8662,7 @@
         <v>50</v>
       </c>
       <c r="J156" s="6">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="K156" s="5" t="s">
         <v>37</v>
@@ -8700,7 +8700,7 @@
         <v>56</v>
       </c>
       <c r="J157" s="8">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="K157" s="9" t="s">
         <v>37</v>
@@ -8738,7 +8738,7 @@
         <v>36</v>
       </c>
       <c r="J158" s="6">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K158" s="5" t="s">
         <v>37</v>
@@ -8776,7 +8776,7 @@
         <v>44</v>
       </c>
       <c r="J159" s="8">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K159" s="9" t="s">
         <v>37</v>
@@ -8814,7 +8814,7 @@
         <v>50</v>
       </c>
       <c r="J160" s="6">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="K160" s="5" t="s">
         <v>37</v>
@@ -8852,7 +8852,7 @@
         <v>56</v>
       </c>
       <c r="J161" s="8">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K161" s="9" t="s">
         <v>37</v>
@@ -8890,7 +8890,7 @@
         <v>36</v>
       </c>
       <c r="J162" s="6">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="K162" s="5" t="s">
         <v>37</v>
@@ -8928,7 +8928,7 @@
         <v>44</v>
       </c>
       <c r="J163" s="8">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K163" s="9" t="s">
         <v>37</v>
@@ -8966,7 +8966,7 @@
         <v>50</v>
       </c>
       <c r="J164" s="6">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K164" s="5" t="s">
         <v>37</v>
@@ -9004,7 +9004,7 @@
         <v>56</v>
       </c>
       <c r="J165" s="8">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="K165" s="9" t="s">
         <v>37</v>
@@ -9042,7 +9042,7 @@
         <v>36</v>
       </c>
       <c r="J166" s="6">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="K166" s="5" t="s">
         <v>37</v>
@@ -9080,7 +9080,7 @@
         <v>44</v>
       </c>
       <c r="J167" s="8">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="K167" s="9" t="s">
         <v>37</v>
@@ -9118,7 +9118,7 @@
         <v>50</v>
       </c>
       <c r="J168" s="6">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="K168" s="5" t="s">
         <v>37</v>
@@ -9156,7 +9156,7 @@
         <v>56</v>
       </c>
       <c r="J169" s="8">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="K169" s="9" t="s">
         <v>37</v>
@@ -9194,7 +9194,7 @@
         <v>36</v>
       </c>
       <c r="J170" s="6">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="K170" s="5" t="s">
         <v>37</v>
@@ -9232,7 +9232,7 @@
         <v>44</v>
       </c>
       <c r="J171" s="8">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="K171" s="9" t="s">
         <v>37</v>
@@ -9270,7 +9270,7 @@
         <v>50</v>
       </c>
       <c r="J172" s="6">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="K172" s="5" t="s">
         <v>37</v>
@@ -9308,7 +9308,7 @@
         <v>56</v>
       </c>
       <c r="J173" s="8">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="K173" s="9" t="s">
         <v>37</v>
@@ -9346,7 +9346,7 @@
         <v>36</v>
       </c>
       <c r="J174" s="6">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="K174" s="5" t="s">
         <v>37</v>
@@ -9384,7 +9384,7 @@
         <v>44</v>
       </c>
       <c r="J175" s="8">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="K175" s="9" t="s">
         <v>37</v>
@@ -9422,7 +9422,7 @@
         <v>50</v>
       </c>
       <c r="J176" s="6">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="K176" s="5" t="s">
         <v>37</v>
@@ -9460,7 +9460,7 @@
         <v>56</v>
       </c>
       <c r="J177" s="8">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="K177" s="9" t="s">
         <v>37</v>
@@ -9498,7 +9498,7 @@
         <v>36</v>
       </c>
       <c r="J178" s="6">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K178" s="5" t="s">
         <v>37</v>
@@ -9536,7 +9536,7 @@
         <v>44</v>
       </c>
       <c r="J179" s="8">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K179" s="9" t="s">
         <v>37</v>
@@ -9574,7 +9574,7 @@
         <v>50</v>
       </c>
       <c r="J180" s="6">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="K180" s="5" t="s">
         <v>37</v>
@@ -9612,7 +9612,7 @@
         <v>56</v>
       </c>
       <c r="J181" s="8">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="K181" s="9" t="s">
         <v>37</v>
@@ -9650,7 +9650,7 @@
         <v>36</v>
       </c>
       <c r="J182" s="6">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="K182" s="5" t="s">
         <v>37</v>
@@ -9688,7 +9688,7 @@
         <v>44</v>
       </c>
       <c r="J183" s="8">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="K183" s="9" t="s">
         <v>37</v>
@@ -9726,7 +9726,7 @@
         <v>50</v>
       </c>
       <c r="J184" s="6">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="K184" s="5" t="s">
         <v>37</v>
@@ -9764,7 +9764,7 @@
         <v>56</v>
       </c>
       <c r="J185" s="8">
-        <v>60</v>
+        <v>146</v>
       </c>
       <c r="K185" s="9" t="s">
         <v>37</v>
@@ -9802,7 +9802,7 @@
         <v>36</v>
       </c>
       <c r="J186" s="6">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="K186" s="5" t="s">
         <v>37</v>
@@ -9840,7 +9840,7 @@
         <v>44</v>
       </c>
       <c r="J187" s="8">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="K187" s="9" t="s">
         <v>37</v>
@@ -9878,7 +9878,7 @@
         <v>50</v>
       </c>
       <c r="J188" s="6">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="K188" s="5" t="s">
         <v>37</v>
@@ -9916,7 +9916,7 @@
         <v>56</v>
       </c>
       <c r="J189" s="8">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="K189" s="9" t="s">
         <v>37</v>
@@ -9954,7 +9954,7 @@
         <v>36</v>
       </c>
       <c r="J190" s="6">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="K190" s="5" t="s">
         <v>37</v>
@@ -9992,7 +9992,7 @@
         <v>44</v>
       </c>
       <c r="J191" s="8">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K191" s="9" t="s">
         <v>37</v>
@@ -10030,7 +10030,7 @@
         <v>50</v>
       </c>
       <c r="J192" s="6">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="K192" s="5" t="s">
         <v>37</v>
@@ -10068,7 +10068,7 @@
         <v>56</v>
       </c>
       <c r="J193" s="8">
-        <v>58</v>
+        <v>124</v>
       </c>
       <c r="K193" s="9" t="s">
         <v>37</v>
@@ -10106,7 +10106,7 @@
         <v>36</v>
       </c>
       <c r="J194" s="6">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="K194" s="5" t="s">
         <v>37</v>
@@ -10144,7 +10144,7 @@
         <v>44</v>
       </c>
       <c r="J195" s="8">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="K195" s="9" t="s">
         <v>37</v>
@@ -10182,7 +10182,7 @@
         <v>50</v>
       </c>
       <c r="J196" s="6">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K196" s="5" t="s">
         <v>37</v>
@@ -10220,7 +10220,7 @@
         <v>56</v>
       </c>
       <c r="J197" s="8">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="K197" s="9" t="s">
         <v>37</v>
@@ -10258,7 +10258,7 @@
         <v>36</v>
       </c>
       <c r="J198" s="6">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="K198" s="5" t="s">
         <v>37</v>
@@ -10296,7 +10296,7 @@
         <v>44</v>
       </c>
       <c r="J199" s="8">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="K199" s="9" t="s">
         <v>37</v>
@@ -10334,7 +10334,7 @@
         <v>50</v>
       </c>
       <c r="J200" s="6">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="K200" s="5" t="s">
         <v>37</v>
@@ -10372,7 +10372,7 @@
         <v>56</v>
       </c>
       <c r="J201" s="8">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="K201" s="9" t="s">
         <v>37</v>
@@ -10410,7 +10410,7 @@
         <v>36</v>
       </c>
       <c r="J202" s="6">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="K202" s="5" t="s">
         <v>37</v>
@@ -10448,7 +10448,7 @@
         <v>44</v>
       </c>
       <c r="J203" s="8">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="K203" s="9" t="s">
         <v>37</v>
@@ -10486,7 +10486,7 @@
         <v>50</v>
       </c>
       <c r="J204" s="6">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="K204" s="5" t="s">
         <v>37</v>
@@ -10524,7 +10524,7 @@
         <v>56</v>
       </c>
       <c r="J205" s="8">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="K205" s="9" t="s">
         <v>37</v>
@@ -10562,7 +10562,7 @@
         <v>36</v>
       </c>
       <c r="J206" s="6">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="K206" s="5" t="s">
         <v>37</v>
@@ -10600,7 +10600,7 @@
         <v>44</v>
       </c>
       <c r="J207" s="8">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="K207" s="9" t="s">
         <v>37</v>
@@ -10638,7 +10638,7 @@
         <v>50</v>
       </c>
       <c r="J208" s="6">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="K208" s="5" t="s">
         <v>37</v>
@@ -10676,7 +10676,7 @@
         <v>56</v>
       </c>
       <c r="J209" s="8">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="K209" s="9" t="s">
         <v>37</v>
@@ -10714,7 +10714,7 @@
         <v>36</v>
       </c>
       <c r="J210" s="6">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="K210" s="5" t="s">
         <v>37</v>
@@ -10752,7 +10752,7 @@
         <v>44</v>
       </c>
       <c r="J211" s="8">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="K211" s="9" t="s">
         <v>37</v>
@@ -10790,7 +10790,7 @@
         <v>50</v>
       </c>
       <c r="J212" s="6">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="K212" s="5" t="s">
         <v>37</v>
@@ -10828,7 +10828,7 @@
         <v>56</v>
       </c>
       <c r="J213" s="8">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="K213" s="9" t="s">
         <v>37</v>
@@ -10866,7 +10866,7 @@
         <v>36</v>
       </c>
       <c r="J214" s="6">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="K214" s="5" t="s">
         <v>37</v>
@@ -10904,7 +10904,7 @@
         <v>44</v>
       </c>
       <c r="J215" s="8">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="K215" s="9" t="s">
         <v>37</v>
@@ -10942,7 +10942,7 @@
         <v>50</v>
       </c>
       <c r="J216" s="6">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K216" s="5" t="s">
         <v>37</v>
@@ -10980,7 +10980,7 @@
         <v>56</v>
       </c>
       <c r="J217" s="8">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="K217" s="9" t="s">
         <v>37</v>
@@ -11018,7 +11018,7 @@
         <v>36</v>
       </c>
       <c r="J218" s="6">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="K218" s="5" t="s">
         <v>37</v>
@@ -11056,7 +11056,7 @@
         <v>44</v>
       </c>
       <c r="J219" s="8">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="K219" s="9" t="s">
         <v>37</v>
@@ -11094,7 +11094,7 @@
         <v>50</v>
       </c>
       <c r="J220" s="6">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="K220" s="5" t="s">
         <v>37</v>
@@ -11132,7 +11132,7 @@
         <v>56</v>
       </c>
       <c r="J221" s="8">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K221" s="9" t="s">
         <v>37</v>
@@ -11170,7 +11170,7 @@
         <v>36</v>
       </c>
       <c r="J222" s="6">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="K222" s="5" t="s">
         <v>37</v>
@@ -11208,7 +11208,7 @@
         <v>44</v>
       </c>
       <c r="J223" s="8">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="K223" s="9" t="s">
         <v>37</v>
@@ -11246,7 +11246,7 @@
         <v>50</v>
       </c>
       <c r="J224" s="6">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="K224" s="5" t="s">
         <v>37</v>
@@ -11284,7 +11284,7 @@
         <v>56</v>
       </c>
       <c r="J225" s="8">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="K225" s="9" t="s">
         <v>37</v>
@@ -11322,7 +11322,7 @@
         <v>36</v>
       </c>
       <c r="J226" s="6">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="K226" s="5" t="s">
         <v>37</v>
@@ -11360,7 +11360,7 @@
         <v>44</v>
       </c>
       <c r="J227" s="8">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="K227" s="9" t="s">
         <v>37</v>
@@ -11398,7 +11398,7 @@
         <v>50</v>
       </c>
       <c r="J228" s="6">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K228" s="5" t="s">
         <v>37</v>
@@ -11436,7 +11436,7 @@
         <v>56</v>
       </c>
       <c r="J229" s="8">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="K229" s="9" t="s">
         <v>37</v>
@@ -11474,7 +11474,7 @@
         <v>36</v>
       </c>
       <c r="J230" s="6">
-        <v>54</v>
+        <v>143</v>
       </c>
       <c r="K230" s="5" t="s">
         <v>37</v>
@@ -11512,7 +11512,7 @@
         <v>44</v>
       </c>
       <c r="J231" s="8">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="K231" s="9" t="s">
         <v>37</v>
@@ -11550,7 +11550,7 @@
         <v>50</v>
       </c>
       <c r="J232" s="6">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="K232" s="5" t="s">
         <v>37</v>
@@ -11588,7 +11588,7 @@
         <v>56</v>
       </c>
       <c r="J233" s="8">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="K233" s="9" t="s">
         <v>37</v>
@@ -11626,7 +11626,7 @@
         <v>36</v>
       </c>
       <c r="J234" s="6">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="K234" s="5" t="s">
         <v>37</v>
@@ -11664,7 +11664,7 @@
         <v>44</v>
       </c>
       <c r="J235" s="8">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="K235" s="9" t="s">
         <v>37</v>
@@ -11702,7 +11702,7 @@
         <v>50</v>
       </c>
       <c r="J236" s="6">
-        <v>44</v>
+        <v>146</v>
       </c>
       <c r="K236" s="5" t="s">
         <v>37</v>
@@ -11740,7 +11740,7 @@
         <v>56</v>
       </c>
       <c r="J237" s="8">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K237" s="9" t="s">
         <v>37</v>
@@ -11778,7 +11778,7 @@
         <v>36</v>
       </c>
       <c r="J238" s="6">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="K238" s="5" t="s">
         <v>37</v>
@@ -11816,7 +11816,7 @@
         <v>44</v>
       </c>
       <c r="J239" s="8">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="K239" s="9" t="s">
         <v>37</v>
@@ -11854,7 +11854,7 @@
         <v>50</v>
       </c>
       <c r="J240" s="6">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="K240" s="5" t="s">
         <v>37</v>
@@ -11892,7 +11892,7 @@
         <v>56</v>
       </c>
       <c r="J241" s="8">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K241" s="9" t="s">
         <v>37</v>
@@ -11930,7 +11930,7 @@
         <v>36</v>
       </c>
       <c r="J242" s="6">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="K242" s="5" t="s">
         <v>37</v>
@@ -11968,7 +11968,7 @@
         <v>44</v>
       </c>
       <c r="J243" s="8">
-        <v>146</v>
+        <v>42</v>
       </c>
       <c r="K243" s="9" t="s">
         <v>37</v>
@@ -12006,7 +12006,7 @@
         <v>50</v>
       </c>
       <c r="J244" s="6">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="K244" s="5" t="s">
         <v>37</v>
@@ -12044,7 +12044,7 @@
         <v>56</v>
       </c>
       <c r="J245" s="8">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="K245" s="9" t="s">
         <v>37</v>
@@ -12082,7 +12082,7 @@
         <v>36</v>
       </c>
       <c r="J246" s="6">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="K246" s="5" t="s">
         <v>37</v>
@@ -12120,7 +12120,7 @@
         <v>44</v>
       </c>
       <c r="J247" s="8">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="K247" s="9" t="s">
         <v>37</v>
@@ -12158,7 +12158,7 @@
         <v>50</v>
       </c>
       <c r="J248" s="6">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="K248" s="5" t="s">
         <v>37</v>
@@ -12196,7 +12196,7 @@
         <v>56</v>
       </c>
       <c r="J249" s="8">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="K249" s="9" t="s">
         <v>37</v>
@@ -12234,7 +12234,7 @@
         <v>36</v>
       </c>
       <c r="J250" s="6">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="K250" s="5" t="s">
         <v>37</v>
@@ -12272,7 +12272,7 @@
         <v>44</v>
       </c>
       <c r="J251" s="8">
-        <v>45</v>
+        <v>147</v>
       </c>
       <c r="K251" s="9" t="s">
         <v>37</v>
@@ -12310,7 +12310,7 @@
         <v>50</v>
       </c>
       <c r="J252" s="6">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="K252" s="5" t="s">
         <v>37</v>
@@ -12348,7 +12348,7 @@
         <v>56</v>
       </c>
       <c r="J253" s="8">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="K253" s="9" t="s">
         <v>37</v>
@@ -12386,7 +12386,7 @@
         <v>36</v>
       </c>
       <c r="J254" s="6">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="K254" s="5" t="s">
         <v>37</v>
@@ -12424,7 +12424,7 @@
         <v>44</v>
       </c>
       <c r="J255" s="8">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c r="K255" s="9" t="s">
         <v>37</v>
@@ -12462,7 +12462,7 @@
         <v>50</v>
       </c>
       <c r="J256" s="6">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="K256" s="5" t="s">
         <v>37</v>
@@ -12500,7 +12500,7 @@
         <v>56</v>
       </c>
       <c r="J257" s="8">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="K257" s="9" t="s">
         <v>37</v>
@@ -12538,7 +12538,7 @@
         <v>36</v>
       </c>
       <c r="J258" s="6">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="K258" s="5" t="s">
         <v>37</v>
@@ -12576,7 +12576,7 @@
         <v>44</v>
       </c>
       <c r="J259" s="8">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="K259" s="9" t="s">
         <v>37</v>
@@ -12614,7 +12614,7 @@
         <v>50</v>
       </c>
       <c r="J260" s="6">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="K260" s="5" t="s">
         <v>37</v>
@@ -12652,7 +12652,7 @@
         <v>56</v>
       </c>
       <c r="J261" s="8">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="K261" s="9" t="s">
         <v>37</v>
@@ -12690,7 +12690,7 @@
         <v>36</v>
       </c>
       <c r="J262" s="6">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="K262" s="5" t="s">
         <v>37</v>
@@ -12728,7 +12728,7 @@
         <v>44</v>
       </c>
       <c r="J263" s="8">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="K263" s="9" t="s">
         <v>37</v>
@@ -12766,7 +12766,7 @@
         <v>50</v>
       </c>
       <c r="J264" s="6">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="K264" s="5" t="s">
         <v>37</v>
@@ -12804,7 +12804,7 @@
         <v>56</v>
       </c>
       <c r="J265" s="8">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="K265" s="9" t="s">
         <v>37</v>
@@ -12842,7 +12842,7 @@
         <v>36</v>
       </c>
       <c r="J266" s="6">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K266" s="5" t="s">
         <v>37</v>
@@ -12880,7 +12880,7 @@
         <v>44</v>
       </c>
       <c r="J267" s="8">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="K267" s="9" t="s">
         <v>37</v>
@@ -12918,7 +12918,7 @@
         <v>50</v>
       </c>
       <c r="J268" s="6">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="K268" s="5" t="s">
         <v>37</v>
@@ -12956,7 +12956,7 @@
         <v>56</v>
       </c>
       <c r="J269" s="8">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="K269" s="9" t="s">
         <v>37</v>
@@ -12994,7 +12994,7 @@
         <v>36</v>
       </c>
       <c r="J270" s="6">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="K270" s="5" t="s">
         <v>37</v>
@@ -13032,7 +13032,7 @@
         <v>44</v>
       </c>
       <c r="J271" s="8">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="K271" s="9" t="s">
         <v>37</v>
@@ -13070,7 +13070,7 @@
         <v>50</v>
       </c>
       <c r="J272" s="6">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K272" s="5" t="s">
         <v>37</v>
@@ -13108,7 +13108,7 @@
         <v>56</v>
       </c>
       <c r="J273" s="8">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K273" s="9" t="s">
         <v>37</v>
@@ -13146,7 +13146,7 @@
         <v>36</v>
       </c>
       <c r="J274" s="6">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="K274" s="5" t="s">
         <v>37</v>
@@ -13184,7 +13184,7 @@
         <v>44</v>
       </c>
       <c r="J275" s="8">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="K275" s="9" t="s">
         <v>37</v>
@@ -13222,7 +13222,7 @@
         <v>50</v>
       </c>
       <c r="J276" s="6">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="K276" s="5" t="s">
         <v>37</v>
@@ -13260,7 +13260,7 @@
         <v>56</v>
       </c>
       <c r="J277" s="8">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="K277" s="9" t="s">
         <v>37</v>
@@ -13298,7 +13298,7 @@
         <v>36</v>
       </c>
       <c r="J278" s="6">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="K278" s="5" t="s">
         <v>37</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="J279" s="8">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="K279" s="9" t="s">
         <v>37</v>
@@ -13374,7 +13374,7 @@
         <v>50</v>
       </c>
       <c r="J280" s="6">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="K280" s="5" t="s">
         <v>37</v>
@@ -13412,7 +13412,7 @@
         <v>56</v>
       </c>
       <c r="J281" s="8">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="K281" s="9" t="s">
         <v>37</v>
@@ -13450,7 +13450,7 @@
         <v>36</v>
       </c>
       <c r="J282" s="6">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="K282" s="5" t="s">
         <v>37</v>
@@ -13488,7 +13488,7 @@
         <v>44</v>
       </c>
       <c r="J283" s="8">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="K283" s="9" t="s">
         <v>37</v>
@@ -13526,7 +13526,7 @@
         <v>50</v>
       </c>
       <c r="J284" s="6">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="K284" s="5" t="s">
         <v>37</v>
@@ -13564,7 +13564,7 @@
         <v>56</v>
       </c>
       <c r="J285" s="8">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="K285" s="9" t="s">
         <v>37</v>
@@ -13602,7 +13602,7 @@
         <v>36</v>
       </c>
       <c r="J286" s="6">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="K286" s="5" t="s">
         <v>37</v>
@@ -13640,7 +13640,7 @@
         <v>44</v>
       </c>
       <c r="J287" s="8">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="K287" s="9" t="s">
         <v>37</v>
@@ -13678,7 +13678,7 @@
         <v>50</v>
       </c>
       <c r="J288" s="6">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="K288" s="5" t="s">
         <v>37</v>
@@ -13716,7 +13716,7 @@
         <v>56</v>
       </c>
       <c r="J289" s="8">
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="K289" s="9" t="s">
         <v>37</v>
@@ -13754,7 +13754,7 @@
         <v>36</v>
       </c>
       <c r="J290" s="6">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="K290" s="5" t="s">
         <v>37</v>
@@ -13792,7 +13792,7 @@
         <v>44</v>
       </c>
       <c r="J291" s="8">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="K291" s="9" t="s">
         <v>37</v>
@@ -13830,7 +13830,7 @@
         <v>50</v>
       </c>
       <c r="J292" s="6">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="K292" s="5" t="s">
         <v>37</v>
@@ -13868,7 +13868,7 @@
         <v>56</v>
       </c>
       <c r="J293" s="8">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="K293" s="9" t="s">
         <v>37</v>
@@ -13906,7 +13906,7 @@
         <v>36</v>
       </c>
       <c r="J294" s="6">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="K294" s="5" t="s">
         <v>37</v>
@@ -13944,7 +13944,7 @@
         <v>44</v>
       </c>
       <c r="J295" s="8">
-        <v>143</v>
+        <v>57</v>
       </c>
       <c r="K295" s="9" t="s">
         <v>37</v>
@@ -13982,7 +13982,7 @@
         <v>50</v>
       </c>
       <c r="J296" s="6">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="K296" s="5" t="s">
         <v>37</v>
@@ -14020,7 +14020,7 @@
         <v>56</v>
       </c>
       <c r="J297" s="8">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="K297" s="9" t="s">
         <v>37</v>
@@ -14058,7 +14058,7 @@
         <v>36</v>
       </c>
       <c r="J298" s="6">
-        <v>149</v>
+        <v>47</v>
       </c>
       <c r="K298" s="5" t="s">
         <v>37</v>
@@ -14096,7 +14096,7 @@
         <v>44</v>
       </c>
       <c r="J299" s="8">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="K299" s="9" t="s">
         <v>37</v>
@@ -14134,7 +14134,7 @@
         <v>50</v>
       </c>
       <c r="J300" s="6">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="K300" s="5" t="s">
         <v>37</v>
@@ -14172,7 +14172,7 @@
         <v>56</v>
       </c>
       <c r="J301" s="8">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="K301" s="9" t="s">
         <v>37</v>
